--- a/반응성 염료 상용성 실험.xlsx
+++ b/반응성 염료 상용성 실험.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\상용성 프로그램\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\Ohyoung Dye Finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8B5C41-043B-4683-BBF0-69ED0E6B50F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1548A5A-047F-4DE7-A492-264912F21232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="420" windowWidth="15570" windowHeight="15225" tabRatio="802" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="802" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="그래프" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,11 @@
     <sheet name="H-E SREF" sheetId="9" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Blue!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Navy Blue'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Other!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Red!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Yellow!$B$1:$K$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'H-E SREF'!$A$1:$N$71</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">SREF!$A$1:$N$73</definedName>
   </definedNames>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="295">
   <si>
     <t>Sunfix Red FE-6BA</t>
   </si>
@@ -735,36 +740,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Y H-E6GN</t>
-  </si>
-  <si>
-    <t>Y H-E4G</t>
-  </si>
-  <si>
-    <t>O H-ER</t>
-  </si>
-  <si>
-    <t>TQ H-A</t>
-  </si>
-  <si>
-    <t>Gr H-E4BD</t>
-  </si>
-  <si>
-    <t>NB H-ER 150%</t>
-  </si>
-  <si>
-    <t>BK H-EM</t>
-  </si>
-  <si>
-    <t>Y H-EL</t>
-  </si>
-  <si>
-    <t>Crimson H-EL</t>
-  </si>
-  <si>
-    <t>NB H-ELN</t>
-  </si>
-  <si>
     <t>Suncion Yellow H-E6GN</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -870,9 +845,6 @@
     <t>Red H-E7B</t>
   </si>
   <si>
-    <t>Red H-EGL</t>
-  </si>
-  <si>
     <t>Blue H-ERD 125%</t>
   </si>
   <si>
@@ -922,10 +894,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Red SPD conc.(K)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>N</t>
     </r>
@@ -946,32 +914,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Y H-E4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Sunfix Amber HP</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1012,26 +954,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/SN-2BL(1.0%)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R/SN-2BL(1.0% saltx2)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>R/SN-2BL 1.0%</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1224,6 +1146,174 @@
         <charset val="129"/>
       </rPr>
       <t>avy Blue CU</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>ellow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> H-E6GN</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>ellow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> H-E4G</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yellow H-E4RN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>range</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> H-ER</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Turquoise Blue H-A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green H-E4BD</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>avy Blue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> H-ER 150%</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black H-EM</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>ellow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> H-EL</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Red H-EGL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crimson H-EL</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>avy Blue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+      </rPr>
+      <t xml:space="preserve"> H-ELN</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2965,7 +3055,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -3000,7 +3090,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1">
@@ -3355,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D3" s="15">
         <v>53.326125201583352</v>
@@ -3383,7 +3473,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D4" s="15">
         <v>60.449711875482684</v>
@@ -3411,7 +3501,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D5" s="15">
         <v>47.726825326108354</v>
@@ -3439,7 +3529,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D6" s="15">
         <v>66.234610716143578</v>
@@ -3467,7 +3557,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="D7" s="15">
         <v>72.740535240236298</v>
@@ -3495,7 +3585,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D8" s="15">
         <v>67.346857991093515</v>
@@ -3523,7 +3613,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D9" s="15">
         <v>75.641274887641103</v>
@@ -3551,7 +3641,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D10" s="15">
         <v>74.171757810559782</v>
@@ -3579,7 +3669,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D11" s="15">
         <v>72.935607928212221</v>
@@ -3607,7 +3697,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D12" s="15">
         <v>84.979583204542138</v>
@@ -3635,7 +3725,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D13" s="15">
         <v>81.381489480841523</v>
@@ -3663,7 +3753,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D14" s="15">
         <v>56.908768821966341</v>
@@ -3691,7 +3781,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D15" s="15">
         <v>71.465569456337846</v>
@@ -3719,7 +3809,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D16" s="15">
         <v>70.325998370008151</v>
@@ -3747,7 +3837,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D17" s="15">
         <v>55.444695259593679</v>
@@ -3775,7 +3865,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D18" s="15">
         <v>65.58444744265914</v>
@@ -4726,7 +4816,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
@@ -4738,7 +4828,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1">
@@ -4769,23 +4859,24 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>281</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="21">
-        <v>24</v>
+        <v>16.5533</v>
       </c>
       <c r="F2" s="21">
-        <v>30</v>
+        <v>20.811199999999999</v>
       </c>
       <c r="G2" s="21"/>
       <c r="H2" s="21">
-        <v>65</v>
+        <v>40.44</v>
       </c>
       <c r="I2" s="21">
-        <v>93</v>
+        <v>85.11</v>
       </c>
       <c r="J2" s="21">
         <v>100</v>
@@ -4798,25 +4889,25 @@
       <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>169</v>
+      <c r="B3" s="23" t="s">
+        <v>96</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3" s="21">
-        <v>25.194400000000002</v>
+        <v>53.399500000000003</v>
       </c>
       <c r="F3" s="21">
-        <v>31.6751</v>
+        <v>67.135400000000004</v>
       </c>
       <c r="G3" s="21"/>
       <c r="H3" s="21">
-        <v>22.07</v>
+        <v>65.8</v>
       </c>
       <c r="I3" s="21">
-        <v>80.517499999999998</v>
+        <v>91.45</v>
       </c>
       <c r="J3" s="21">
         <v>100</v>
@@ -4830,24 +4921,24 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="21">
-        <v>16.5533</v>
+        <v>35.7303</v>
       </c>
       <c r="F4" s="21">
-        <v>20.811199999999999</v>
+        <v>44.921100000000003</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21">
-        <v>40.44</v>
+        <v>50.06</v>
       </c>
       <c r="I4" s="21">
-        <v>85.11</v>
+        <v>87.515000000000001</v>
       </c>
       <c r="J4" s="21">
         <v>100</v>
@@ -4861,24 +4952,24 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <v>44.628399999999999</v>
+        <v>45.534300000000002</v>
       </c>
       <c r="F5" s="21">
-        <v>56.1081</v>
+        <v>57.247100000000003</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21">
-        <v>39.03</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="I5" s="21">
-        <v>84.757499999999993</v>
+        <v>88.817499999999995</v>
       </c>
       <c r="J5" s="21">
         <v>100</v>
@@ -4892,24 +4983,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <v>45.534300000000002</v>
+        <v>31.674600000000002</v>
       </c>
       <c r="F6" s="21">
-        <v>57.247100000000003</v>
+        <v>39.822200000000002</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21">
-        <v>33.909999999999997</v>
+        <v>25.79</v>
       </c>
       <c r="I6" s="21">
-        <v>88.817499999999995</v>
+        <v>81.447500000000005</v>
       </c>
       <c r="J6" s="21">
         <v>100</v>
@@ -4922,25 +5013,25 @@
       <c r="A7" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>283</v>
+      <c r="B7" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <v>63.9358</v>
+        <v>17.4086</v>
       </c>
       <c r="F7" s="21">
-        <v>80.382000000000005</v>
+        <v>21.886600000000001</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21">
-        <v>57.77</v>
+        <v>30.1</v>
       </c>
       <c r="I7" s="21">
-        <v>89.442499999999995</v>
+        <v>82.525000000000006</v>
       </c>
       <c r="J7" s="21">
         <v>100</v>
@@ -4954,24 +5045,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="21">
-        <v>49.606299999999997</v>
+        <v>49.3626</v>
       </c>
       <c r="F8" s="21">
-        <v>62.366500000000002</v>
+        <v>62.060099999999998</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="21">
-        <v>58.47</v>
+        <v>55.76</v>
       </c>
       <c r="I8" s="21">
-        <v>89.617500000000007</v>
+        <v>88.94</v>
       </c>
       <c r="J8" s="21">
         <v>100</v>
@@ -4984,25 +5075,25 @@
       <c r="A9" s="16">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>138</v>
+      <c r="B9" s="23" t="s">
+        <v>268</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="21">
-        <v>45.043399999999998</v>
+        <v>63.9358</v>
       </c>
       <c r="F9" s="21">
-        <v>56.629899999999999</v>
+        <v>80.382000000000005</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21">
-        <v>38.119999999999997</v>
+        <v>57.77</v>
       </c>
       <c r="I9" s="21">
-        <v>84.53</v>
+        <v>89.442499999999995</v>
       </c>
       <c r="J9" s="21">
         <v>100</v>
@@ -5015,30 +5106,30 @@
       <c r="A10" s="16">
         <v>9</v>
       </c>
-      <c r="B10" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25">
-        <v>45.534300000000002</v>
-      </c>
-      <c r="F10" s="25">
-        <v>57.247100000000003</v>
-      </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25">
-        <v>55.27</v>
-      </c>
-      <c r="I10" s="25">
-        <v>88.817499999999995</v>
-      </c>
-      <c r="J10" s="25">
-        <v>100</v>
-      </c>
-      <c r="K10" s="25">
+      <c r="B10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21">
+        <v>45.3566</v>
+      </c>
+      <c r="F10" s="21">
+        <v>57.023699999999998</v>
+      </c>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21">
+        <v>33.909999999999997</v>
+      </c>
+      <c r="I10" s="21">
+        <v>83.477500000000006</v>
+      </c>
+      <c r="J10" s="21">
+        <v>100</v>
+      </c>
+      <c r="K10" s="21">
         <v>100</v>
       </c>
     </row>
@@ -5046,30 +5137,30 @@
       <c r="A11" s="16">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
-        <v>49.3626</v>
-      </c>
-      <c r="F11" s="21">
-        <v>62.060099999999998</v>
-      </c>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21">
-        <v>55.76</v>
-      </c>
-      <c r="I11" s="21">
-        <v>88.94</v>
-      </c>
-      <c r="J11" s="21">
-        <v>100</v>
-      </c>
-      <c r="K11" s="21">
+      <c r="B11" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25">
+        <v>45.534300000000002</v>
+      </c>
+      <c r="F11" s="25">
+        <v>57.247100000000003</v>
+      </c>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25">
+        <v>55.27</v>
+      </c>
+      <c r="I11" s="25">
+        <v>88.817499999999995</v>
+      </c>
+      <c r="J11" s="25">
+        <v>100</v>
+      </c>
+      <c r="K11" s="25">
         <v>100</v>
       </c>
     </row>
@@ -5078,24 +5169,24 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="21">
-        <v>45.3566</v>
+        <v>25.194400000000002</v>
       </c>
       <c r="F12" s="21">
-        <v>57.023699999999998</v>
+        <v>31.6751</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="21">
-        <v>33.909999999999997</v>
+        <v>22.07</v>
       </c>
       <c r="I12" s="21">
-        <v>83.477500000000006</v>
+        <v>80.517499999999998</v>
       </c>
       <c r="J12" s="21">
         <v>100</v>
@@ -5108,25 +5199,25 @@
       <c r="A13" s="16">
         <v>12</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>96</v>
+      <c r="B13" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="21">
-        <v>53.399500000000003</v>
+        <v>49.606299999999997</v>
       </c>
       <c r="F13" s="21">
-        <v>67.135400000000004</v>
+        <v>62.366500000000002</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21">
-        <v>65.8</v>
+        <v>58.47</v>
       </c>
       <c r="I13" s="21">
-        <v>91.45</v>
+        <v>89.617500000000007</v>
       </c>
       <c r="J13" s="21">
         <v>100</v>
@@ -5140,24 +5231,24 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="21">
-        <v>35.7303</v>
+        <v>45.043399999999998</v>
       </c>
       <c r="F14" s="21">
-        <v>44.921100000000003</v>
+        <v>56.629899999999999</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21">
-        <v>50.06</v>
+        <v>38.119999999999997</v>
       </c>
       <c r="I14" s="21">
-        <v>87.515000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="J14" s="21">
         <v>100</v>
@@ -5171,24 +5262,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="21">
-        <v>31.674600000000002</v>
+        <v>45.534300000000002</v>
       </c>
       <c r="F15" s="21">
-        <v>39.822200000000002</v>
+        <v>57.247100000000003</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21">
-        <v>25.79</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="I15" s="21">
-        <v>81.447500000000005</v>
+        <v>88.817499999999995</v>
       </c>
       <c r="J15" s="21">
         <v>100</v>
@@ -5201,25 +5292,25 @@
       <c r="A16" s="16">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>41</v>
+      <c r="B16" s="19" t="s">
+        <v>264</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="21">
-        <v>45.534300000000002</v>
+        <v>49.3626</v>
       </c>
       <c r="F16" s="21">
-        <v>57.247100000000003</v>
+        <v>62.060099999999998</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="21">
-        <v>33.909999999999997</v>
+        <v>55.76</v>
       </c>
       <c r="I16" s="21">
-        <v>88.817499999999995</v>
+        <v>88.94</v>
       </c>
       <c r="J16" s="21">
         <v>100</v>
@@ -5233,24 +5324,24 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="21">
-        <v>49.3626</v>
+        <v>44.628399999999999</v>
       </c>
       <c r="F17" s="21">
-        <v>62.060099999999998</v>
+        <v>56.1081</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21">
-        <v>55.76</v>
+        <v>39.03</v>
       </c>
       <c r="I17" s="21">
-        <v>88.94</v>
+        <v>84.757499999999993</v>
       </c>
       <c r="J17" s="21">
         <v>100</v>
@@ -5264,24 +5355,24 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="21">
-        <v>17.4086</v>
+        <v>40.897100000000002</v>
       </c>
       <c r="F18" s="21">
-        <v>21.886600000000001</v>
+        <v>51.417099999999998</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21">
-        <v>30.1</v>
+        <v>39.1</v>
       </c>
       <c r="I18" s="21">
-        <v>82.525000000000006</v>
+        <v>84.775000000000006</v>
       </c>
       <c r="J18" s="21">
         <v>100</v>
@@ -5295,24 +5386,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>265</v>
+      </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="21">
-        <v>23.502400000000002</v>
+        <v>64</v>
       </c>
       <c r="F19" s="21">
-        <v>29.547899999999998</v>
+        <v>78</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21">
-        <v>43.37</v>
+        <v>77</v>
       </c>
       <c r="I19" s="21">
-        <v>85.842500000000001</v>
+        <v>96</v>
       </c>
       <c r="J19" s="21">
         <v>100</v>
@@ -5326,24 +5416,24 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="21">
-        <v>40.897100000000002</v>
+        <v>15.5136</v>
       </c>
       <c r="F20" s="21">
-        <v>51.417099999999998</v>
+        <v>19.504100000000001</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21">
-        <v>39.1</v>
+        <v>58.11</v>
       </c>
       <c r="I20" s="21">
-        <v>84.775000000000006</v>
+        <v>89.527500000000003</v>
       </c>
       <c r="J20" s="21">
         <v>100</v>
@@ -5357,24 +5447,24 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="21">
-        <v>15.5136</v>
+        <v>23.502400000000002</v>
       </c>
       <c r="F21" s="21">
-        <v>19.504100000000001</v>
+        <v>29.547899999999998</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="21">
-        <v>58.11</v>
+        <v>43.37</v>
       </c>
       <c r="I21" s="21">
-        <v>89.527500000000003</v>
+        <v>85.842500000000001</v>
       </c>
       <c r="J21" s="21">
         <v>100</v>
@@ -5388,23 +5478,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="21">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="F22" s="21">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="21">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I22" s="21">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J22" s="21">
         <v>100</v>
@@ -5418,24 +5508,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="21">
-        <v>25.299299999999999</v>
+        <v>21.648700000000002</v>
       </c>
       <c r="F23" s="21">
-        <v>31.806999999999999</v>
+        <v>27.217300000000002</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="21">
-        <v>52.43</v>
+        <v>36.770000000000003</v>
       </c>
       <c r="I23" s="21">
-        <v>88.107500000000002</v>
+        <v>84.192499999999995</v>
       </c>
       <c r="J23" s="21">
         <v>100</v>
@@ -5448,25 +5538,25 @@
       <c r="A24" s="16">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>81</v>
+      <c r="B24" s="23" t="s">
+        <v>232</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="21">
-        <v>26.4437</v>
+        <v>51.542499999999997</v>
       </c>
       <c r="F24" s="21">
-        <v>33.245800000000003</v>
+        <v>64.800799999999995</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="21">
-        <v>65.08</v>
+        <v>67.22</v>
       </c>
       <c r="I24" s="21">
-        <v>91.27</v>
+        <v>91.805000000000007</v>
       </c>
       <c r="J24" s="21">
         <v>100</v>
@@ -5480,24 +5570,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="21">
-        <v>25.522500000000001</v>
+        <v>25.299299999999999</v>
       </c>
       <c r="F25" s="21">
-        <v>32.087699999999998</v>
+        <v>31.806999999999999</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="21">
-        <v>67.72</v>
+        <v>52.43</v>
       </c>
       <c r="I25" s="21">
-        <v>91.93</v>
+        <v>88.107500000000002</v>
       </c>
       <c r="J25" s="21">
         <v>100</v>
@@ -5511,24 +5601,24 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="21">
-        <v>66.407600000000002</v>
+        <v>25.522500000000001</v>
       </c>
       <c r="F26" s="21">
-        <v>83.489500000000007</v>
+        <v>32.087699999999998</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="21">
-        <v>48.01</v>
+        <v>67.72</v>
       </c>
       <c r="I26" s="21">
-        <v>87.002499999999998</v>
+        <v>91.93</v>
       </c>
       <c r="J26" s="21">
         <v>100</v>
@@ -5542,24 +5632,24 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="21">
-        <v>64.935599999999994</v>
+        <v>25.522500000000001</v>
       </c>
       <c r="F27" s="21">
-        <v>81.638900000000007</v>
+        <v>32.087699999999998</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="21">
-        <v>70.37</v>
+        <v>67.72</v>
       </c>
       <c r="I27" s="21">
-        <v>92.592500000000001</v>
+        <v>91.93</v>
       </c>
       <c r="J27" s="21">
         <v>100</v>
@@ -5573,24 +5663,24 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="21">
-        <v>21.648700000000002</v>
+        <v>66.407600000000002</v>
       </c>
       <c r="F28" s="21">
-        <v>27.217300000000002</v>
+        <v>83.489500000000007</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="21">
-        <v>36.770000000000003</v>
+        <v>48.01</v>
       </c>
       <c r="I28" s="21">
-        <v>84.192499999999995</v>
+        <v>87.002499999999998</v>
       </c>
       <c r="J28" s="21">
         <v>100</v>
@@ -5603,25 +5693,25 @@
       <c r="A29" s="16">
         <v>28</v>
       </c>
-      <c r="B29" s="23" t="s">
-        <v>242</v>
+      <c r="B29" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="21">
-        <v>51.542499999999997</v>
+        <v>64.935599999999994</v>
       </c>
       <c r="F29" s="21">
-        <v>64.800799999999995</v>
+        <v>81.638900000000007</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="21">
-        <v>67.22</v>
+        <v>70.37</v>
       </c>
       <c r="I29" s="21">
-        <v>91.805000000000007</v>
+        <v>92.592500000000001</v>
       </c>
       <c r="J29" s="21">
         <v>100</v>
@@ -5635,7 +5725,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
@@ -5666,24 +5756,24 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="21">
-        <v>25.522500000000001</v>
+        <v>26.4437</v>
       </c>
       <c r="F31" s="21">
-        <v>32.087699999999998</v>
+        <v>33.245800000000003</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="21">
-        <v>67.72</v>
+        <v>65.08</v>
       </c>
       <c r="I31" s="21">
-        <v>91.93</v>
+        <v>91.27</v>
       </c>
       <c r="J31" s="21">
         <v>100</v>
@@ -5692,37 +5782,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="19"/>
-      <c r="C35" s="1"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B37" s="19"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-    </row>
   </sheetData>
+  <autoFilter ref="B1:K1" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:K31">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5732,7 +5797,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.125" style="4" customWidth="1"/>
@@ -5745,7 +5810,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D1" s="1">
         <v>0</v>
@@ -5774,24 +5839,24 @@
         <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="21">
-        <v>54.240299999999998</v>
+        <v>48.580599999999997</v>
       </c>
       <c r="F2" s="21">
-        <v>68.192499999999995</v>
+        <v>61.076900000000002</v>
       </c>
       <c r="G2" s="21"/>
       <c r="H2" s="21">
-        <v>67.239999999999995</v>
+        <v>83.65</v>
       </c>
       <c r="I2" s="21">
-        <v>91.81</v>
+        <v>95.912499999999994</v>
       </c>
       <c r="J2" s="21">
         <v>100</v>
@@ -5805,24 +5870,24 @@
         <v>32</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3" s="21">
-        <v>38.895400000000002</v>
+        <v>48.580599999999997</v>
       </c>
       <c r="F3" s="21">
-        <v>48.900399999999998</v>
+        <v>61.076900000000002</v>
       </c>
       <c r="G3" s="21"/>
       <c r="H3" s="21">
-        <v>33.89</v>
+        <v>83.65</v>
       </c>
       <c r="I3" s="21">
-        <v>83.472499999999997</v>
+        <v>95.912499999999994</v>
       </c>
       <c r="J3" s="21">
         <v>100</v>
@@ -5836,24 +5901,24 @@
         <v>33</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="21">
-        <v>36.665900000000001</v>
+        <v>33.6432</v>
       </c>
       <c r="F4" s="21">
-        <v>46.097499999999997</v>
+        <v>42.297199999999997</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21">
-        <v>37.78</v>
+        <v>61.37</v>
       </c>
       <c r="I4" s="21">
-        <v>84.444999999999993</v>
+        <v>90.342500000000001</v>
       </c>
       <c r="J4" s="21">
         <v>100</v>
@@ -5867,24 +5932,24 @@
         <v>34</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <v>56.967300000000002</v>
+        <v>41</v>
       </c>
       <c r="F5" s="21">
-        <v>71.620999999999995</v>
+        <v>42</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21">
-        <v>53.71</v>
+        <v>52</v>
       </c>
       <c r="I5" s="21">
-        <v>88.427499999999995</v>
+        <v>87</v>
       </c>
       <c r="J5" s="21">
         <v>100</v>
@@ -5929,24 +5994,24 @@
         <v>36</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <v>36.665900000000001</v>
+        <v>36.441800000000001</v>
       </c>
       <c r="F7" s="21">
-        <v>46.097499999999997</v>
+        <v>45.8157</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21">
-        <v>37.78</v>
+        <v>53.81</v>
       </c>
       <c r="I7" s="21">
-        <v>84.444999999999993</v>
+        <v>88.452500000000001</v>
       </c>
       <c r="J7" s="21">
         <v>100</v>
@@ -5960,24 +6025,24 @@
         <v>37</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="21">
-        <v>33.547600000000003</v>
+        <v>36.665900000000001</v>
       </c>
       <c r="F8" s="21">
-        <v>42.177</v>
+        <v>46.097499999999997</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="21">
-        <v>51.67</v>
+        <v>37.78</v>
       </c>
       <c r="I8" s="21">
-        <v>87.917500000000004</v>
+        <v>84.444999999999993</v>
       </c>
       <c r="J8" s="21">
         <v>100</v>
@@ -5991,24 +6056,24 @@
         <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="21">
-        <v>48.580599999999997</v>
+        <v>41.466200000000001</v>
       </c>
       <c r="F9" s="21">
-        <v>61.076900000000002</v>
+        <v>52.1325</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21">
-        <v>83.65</v>
+        <v>82.92</v>
       </c>
       <c r="I9" s="21">
-        <v>95.912499999999994</v>
+        <v>95.73</v>
       </c>
       <c r="J9" s="21">
         <v>100</v>
@@ -6021,25 +6086,25 @@
       <c r="A10">
         <v>39</v>
       </c>
-      <c r="B10" s="23" t="s">
-        <v>26</v>
+      <c r="B10" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="21">
-        <v>49.476599999999998</v>
+        <v>44.933100000000003</v>
       </c>
       <c r="F10" s="21">
-        <v>62.203400000000002</v>
+        <v>56.491199999999999</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="21">
-        <v>66.900000000000006</v>
+        <v>84.7</v>
       </c>
       <c r="I10" s="21">
-        <v>91.724999999999994</v>
+        <v>96.174999999999997</v>
       </c>
       <c r="J10" s="21">
         <v>100</v>
@@ -6052,25 +6117,25 @@
       <c r="A11">
         <v>40</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>71</v>
+      <c r="B11" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="21">
-        <v>44.933100000000003</v>
+        <v>49.476599999999998</v>
       </c>
       <c r="F11" s="21">
-        <v>56.491199999999999</v>
+        <v>62.203400000000002</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21">
-        <v>84.7</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="I11" s="21">
-        <v>96.174999999999997</v>
+        <v>91.724999999999994</v>
       </c>
       <c r="J11" s="21">
         <v>100</v>
@@ -6084,24 +6149,24 @@
         <v>41</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="21">
-        <v>37.041899999999998</v>
+        <v>35.834800000000001</v>
       </c>
       <c r="F12" s="21">
-        <v>46.570099999999996</v>
+        <v>45.052500000000002</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="21">
-        <v>38.119999999999997</v>
+        <v>51.65</v>
       </c>
       <c r="I12" s="21">
-        <v>84.53</v>
+        <v>87.912499999999994</v>
       </c>
       <c r="J12" s="21">
         <v>100</v>
@@ -6115,24 +6180,24 @@
         <v>42</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="21">
-        <v>36.877099999999999</v>
+        <v>38.585900000000002</v>
       </c>
       <c r="F13" s="21">
-        <v>46.362900000000003</v>
+        <v>48.511299999999999</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21">
-        <v>40.799999999999997</v>
+        <v>46.21</v>
       </c>
       <c r="I13" s="21">
-        <v>85.2</v>
+        <v>86.552499999999995</v>
       </c>
       <c r="J13" s="21">
         <v>100</v>
@@ -6146,24 +6211,24 @@
         <v>43</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="21">
-        <v>35.834800000000001</v>
+        <v>41.556899999999999</v>
       </c>
       <c r="F14" s="21">
-        <v>45.052500000000002</v>
+        <v>52.246499999999997</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21">
-        <v>51.65</v>
+        <v>61.16</v>
       </c>
       <c r="I14" s="21">
-        <v>87.912499999999994</v>
+        <v>90.29</v>
       </c>
       <c r="J14" s="21">
         <v>100</v>
@@ -6177,24 +6242,24 @@
         <v>44</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="21">
-        <v>33.6432</v>
+        <v>45.353900000000003</v>
       </c>
       <c r="F15" s="21">
-        <v>42.297199999999997</v>
+        <v>57.020299999999999</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21">
-        <v>61.37</v>
+        <v>67.77</v>
       </c>
       <c r="I15" s="21">
-        <v>90.342500000000001</v>
+        <v>91.942499999999995</v>
       </c>
       <c r="J15" s="21">
         <v>100</v>
@@ -6208,24 +6273,24 @@
         <v>45</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="21">
-        <v>41.466200000000001</v>
+        <v>40.878300000000003</v>
       </c>
       <c r="F16" s="21">
-        <v>52.1325</v>
+        <v>51.3934</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="21">
-        <v>82.92</v>
+        <v>71.94</v>
       </c>
       <c r="I16" s="21">
-        <v>95.73</v>
+        <v>92.984999999999999</v>
       </c>
       <c r="J16" s="21">
         <v>100</v>
@@ -6270,24 +6335,24 @@
         <v>47</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="21">
-        <v>51.4009</v>
+        <v>37.041899999999998</v>
       </c>
       <c r="F18" s="21">
-        <v>64.622699999999995</v>
+        <v>46.570099999999996</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21">
-        <v>52.84</v>
+        <v>38.119999999999997</v>
       </c>
       <c r="I18" s="21">
-        <v>88.21</v>
+        <v>84.53</v>
       </c>
       <c r="J18" s="21">
         <v>100</v>
@@ -6300,25 +6365,25 @@
       <c r="A19">
         <v>48</v>
       </c>
-      <c r="B19" s="23" t="s">
-        <v>88</v>
+      <c r="B19" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="21">
-        <v>43.008499999999998</v>
+        <v>36.665900000000001</v>
       </c>
       <c r="F19" s="21">
-        <v>54.071599999999997</v>
+        <v>46.097499999999997</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21">
-        <v>47.06</v>
+        <v>37.78</v>
       </c>
       <c r="I19" s="21">
-        <v>86.765000000000001</v>
+        <v>84.444999999999993</v>
       </c>
       <c r="J19" s="21">
         <v>100</v>
@@ -6332,24 +6397,24 @@
         <v>49</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="21">
-        <v>36.441800000000001</v>
+        <v>56.967300000000002</v>
       </c>
       <c r="F20" s="21">
-        <v>45.8157</v>
+        <v>71.620999999999995</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21">
-        <v>53.81</v>
+        <v>53.71</v>
       </c>
       <c r="I20" s="21">
-        <v>88.452500000000001</v>
+        <v>88.427499999999995</v>
       </c>
       <c r="J20" s="21">
         <v>100</v>
@@ -6363,24 +6428,24 @@
         <v>50</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="21">
-        <v>45.353900000000003</v>
+        <v>36.877099999999999</v>
       </c>
       <c r="F21" s="21">
-        <v>57.020299999999999</v>
+        <v>46.362900000000003</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="21">
-        <v>67.77</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="I21" s="21">
-        <v>91.942499999999995</v>
+        <v>85.2</v>
       </c>
       <c r="J21" s="21">
         <v>100</v>
@@ -6394,24 +6459,24 @@
         <v>51</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="21">
-        <v>41.556899999999999</v>
+        <v>41</v>
       </c>
       <c r="F22" s="21">
-        <v>52.246499999999997</v>
+        <v>42</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="21">
-        <v>61.16</v>
+        <v>52</v>
       </c>
       <c r="I22" s="21">
-        <v>90.29</v>
+        <v>87</v>
       </c>
       <c r="J22" s="21">
         <v>100</v>
@@ -6424,30 +6489,29 @@
       <c r="A23">
         <v>52</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="1"/>
+      <c r="B23" s="19" t="s">
+        <v>267</v>
+      </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
-      <c r="E23" s="21">
-        <v>38.585900000000002</v>
-      </c>
-      <c r="F23" s="21">
-        <v>48.511299999999999</v>
-      </c>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21">
-        <v>46.21</v>
-      </c>
-      <c r="I23" s="21">
-        <v>86.552499999999995</v>
-      </c>
-      <c r="J23" s="21">
-        <v>100</v>
-      </c>
-      <c r="K23" s="21">
+      <c r="E23" s="29">
+        <v>54.9</v>
+      </c>
+      <c r="F23" s="29">
+        <v>67.2</v>
+      </c>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29">
+        <v>71</v>
+      </c>
+      <c r="I23" s="29">
+        <v>95.1</v>
+      </c>
+      <c r="J23" s="29">
+        <v>100</v>
+      </c>
+      <c r="K23" s="29">
         <v>100</v>
       </c>
     </row>
@@ -6456,23 +6520,24 @@
         <v>53</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C24" s="1"/>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="21">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F24" s="21">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="21">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I24" s="21">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J24" s="21">
         <v>100</v>
@@ -6485,25 +6550,25 @@
       <c r="A25">
         <v>54</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>42</v>
+      <c r="B25" s="23" t="s">
+        <v>88</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="21">
-        <v>40.878300000000003</v>
+        <v>43.008499999999998</v>
       </c>
       <c r="F25" s="21">
-        <v>51.3934</v>
+        <v>54.071599999999997</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="21">
-        <v>71.94</v>
+        <v>47.06</v>
       </c>
       <c r="I25" s="21">
-        <v>92.984999999999999</v>
+        <v>86.765000000000001</v>
       </c>
       <c r="J25" s="21">
         <v>100</v>
@@ -6516,25 +6581,25 @@
       <c r="A26">
         <v>55</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>267</v>
+      <c r="B26" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="21">
-        <v>54</v>
+        <v>36.441800000000001</v>
       </c>
       <c r="F26" s="21">
-        <v>68</v>
+        <v>45.8157</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="21">
-        <v>49</v>
+        <v>53.81</v>
       </c>
       <c r="I26" s="21">
-        <v>90</v>
+        <v>88.452500000000001</v>
       </c>
       <c r="J26" s="21">
         <v>100</v>
@@ -6548,24 +6613,24 @@
         <v>56</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="21">
-        <v>53</v>
+        <v>38.787199999999999</v>
       </c>
       <c r="F27" s="21">
-        <v>67</v>
+        <v>48.764400000000002</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="21">
-        <v>45</v>
+        <v>52.94</v>
       </c>
       <c r="I27" s="21">
-        <v>84</v>
+        <v>88.234999999999999</v>
       </c>
       <c r="J27" s="21">
         <v>100</v>
@@ -6579,24 +6644,24 @@
         <v>57</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="21">
-        <v>41</v>
+        <v>51.4009</v>
       </c>
       <c r="F28" s="21">
-        <v>42</v>
+        <v>64.622699999999995</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="21">
-        <v>52</v>
+        <v>52.84</v>
       </c>
       <c r="I28" s="21">
-        <v>87</v>
+        <v>88.21</v>
       </c>
       <c r="J28" s="21">
         <v>100</v>
@@ -6609,25 +6674,25 @@
       <c r="A29">
         <v>58</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>265</v>
+      <c r="B29" s="19" t="s">
+        <v>254</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="21">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F29" s="21">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="21">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I29" s="21">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J29" s="21">
         <v>100</v>
@@ -6640,29 +6705,29 @@
       <c r="A30">
         <v>59</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>282</v>
+      <c r="B30" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="29">
-        <v>54.9</v>
-      </c>
-      <c r="F30" s="29">
-        <v>67.2</v>
-      </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29">
-        <v>71</v>
-      </c>
-      <c r="I30" s="29">
-        <v>95.1</v>
-      </c>
-      <c r="J30" s="29">
-        <v>100</v>
-      </c>
-      <c r="K30" s="29">
+      <c r="E30" s="21">
+        <v>23</v>
+      </c>
+      <c r="F30" s="21">
+        <v>33</v>
+      </c>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21">
+        <v>57</v>
+      </c>
+      <c r="I30" s="21">
+        <v>90</v>
+      </c>
+      <c r="J30" s="21">
+        <v>100</v>
+      </c>
+      <c r="K30" s="21">
         <v>100</v>
       </c>
     </row>
@@ -6671,24 +6736,24 @@
         <v>60</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="21">
-        <v>36.441800000000001</v>
+        <v>53</v>
       </c>
       <c r="F31" s="21">
-        <v>45.8157</v>
+        <v>67</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="21">
-        <v>53.81</v>
+        <v>45</v>
       </c>
       <c r="I31" s="21">
-        <v>88.452500000000001</v>
+        <v>84</v>
       </c>
       <c r="J31" s="21">
         <v>100</v>
@@ -6702,24 +6767,24 @@
         <v>61</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="21">
-        <v>41</v>
+        <v>48.580599999999997</v>
       </c>
       <c r="F32" s="21">
-        <v>42</v>
+        <v>61.076900000000002</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="21">
-        <v>52</v>
+        <v>83.65</v>
       </c>
       <c r="I32" s="21">
-        <v>87</v>
+        <v>95.912499999999994</v>
       </c>
       <c r="J32" s="21">
         <v>100</v>
@@ -6733,7 +6798,7 @@
         <v>62</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -6764,24 +6829,24 @@
         <v>63</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="21">
-        <v>38.787199999999999</v>
+        <v>38.895400000000002</v>
       </c>
       <c r="F34" s="21">
-        <v>48.764400000000002</v>
+        <v>48.900399999999998</v>
       </c>
       <c r="G34" s="21"/>
       <c r="H34" s="21">
-        <v>52.94</v>
+        <v>33.89</v>
       </c>
       <c r="I34" s="21">
-        <v>88.234999999999999</v>
+        <v>83.472499999999997</v>
       </c>
       <c r="J34" s="21">
         <v>100</v>
@@ -6790,26 +6855,60 @@
         <v>100</v>
       </c>
     </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>64</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="21">
+        <v>54.240299999999998</v>
+      </c>
+      <c r="F35" s="21">
+        <v>68.192499999999995</v>
+      </c>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21">
+        <v>67.239999999999995</v>
+      </c>
+      <c r="I35" s="21">
+        <v>91.81</v>
+      </c>
+      <c r="J35" s="21">
+        <v>100</v>
+      </c>
+      <c r="K35" s="21">
+        <v>100</v>
+      </c>
+    </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B36" s="19" t="s">
-        <v>268</v>
+      <c r="A36">
+        <v>65</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="21">
-        <v>46</v>
+        <v>33.547600000000003</v>
       </c>
       <c r="F36" s="21">
-        <v>49</v>
+        <v>42.177</v>
       </c>
       <c r="G36" s="21"/>
       <c r="H36" s="21">
-        <v>59</v>
+        <v>51.67</v>
       </c>
       <c r="I36" s="21">
-        <v>89</v>
+        <v>87.917500000000004</v>
       </c>
       <c r="J36" s="21">
         <v>100</v>
@@ -6818,60 +6917,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B37" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-      <c r="E37" s="21">
-        <v>60</v>
-      </c>
-      <c r="F37" s="21">
-        <v>63</v>
-      </c>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21">
-        <v>68</v>
-      </c>
-      <c r="I37" s="21">
-        <v>93</v>
-      </c>
-      <c r="J37" s="21">
-        <v>100</v>
-      </c>
-      <c r="K37" s="21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B38" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20">
-        <v>0</v>
-      </c>
-      <c r="E38" s="21">
-        <v>35.046860057379703</v>
-      </c>
-      <c r="F38" s="21">
-        <v>45.844756136436096</v>
-      </c>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21">
-        <v>45.2</v>
-      </c>
-      <c r="I38" s="21">
-        <v>86.37</v>
-      </c>
-      <c r="J38" s="21">
-        <v>100</v>
-      </c>
-      <c r="K38" s="21">
-        <v>100</v>
-      </c>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="19"/>
+      <c r="C46" s="1"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B47" s="19"/>
@@ -6884,18 +6939,12 @@
       <c r="J47" s="21"/>
       <c r="K47" s="21"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="19"/>
-      <c r="C48" s="1"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
-      <c r="K48" s="21"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K34">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6919,7 +6968,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D1" s="1">
         <v>0</v>
@@ -6945,27 +6994,27 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="21">
-        <v>52.380499999999998</v>
+        <v>25.194400000000002</v>
       </c>
       <c r="F2" s="21">
-        <v>65.854299999999995</v>
+        <v>31.6751</v>
       </c>
       <c r="G2" s="21"/>
       <c r="H2" s="21">
-        <v>31.45</v>
+        <v>29.07</v>
       </c>
       <c r="I2" s="21">
-        <v>82.862499999999997</v>
+        <v>82.267499999999998</v>
       </c>
       <c r="J2" s="21">
         <v>100</v>
@@ -6976,27 +7025,27 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3" s="21">
-        <v>25.992799999999999</v>
+        <v>51.510399999999997</v>
       </c>
       <c r="F3" s="21">
-        <v>32.678899999999999</v>
+        <v>64.760300000000001</v>
       </c>
       <c r="G3" s="21"/>
       <c r="H3" s="21">
-        <v>39.1</v>
+        <v>55.77</v>
       </c>
       <c r="I3" s="21">
-        <v>84.775000000000006</v>
+        <v>88.942499999999995</v>
       </c>
       <c r="J3" s="21">
         <v>100</v>
@@ -7007,27 +7056,27 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="21">
-        <v>51.510399999999997</v>
+        <v>46.883299999999998</v>
       </c>
       <c r="F4" s="21">
-        <v>64.760300000000001</v>
+        <v>58.943100000000001</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21">
-        <v>55.77</v>
+        <v>44.17</v>
       </c>
       <c r="I4" s="21">
-        <v>88.942499999999995</v>
+        <v>86.042500000000004</v>
       </c>
       <c r="J4" s="21">
         <v>100</v>
@@ -7038,27 +7087,27 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <v>61.559600000000003</v>
+        <v>32.134500000000003</v>
       </c>
       <c r="F5" s="21">
-        <v>77.394499999999994</v>
+        <v>40.400399999999998</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21">
-        <v>47.15</v>
+        <v>51.23</v>
       </c>
       <c r="I5" s="21">
-        <v>86.787499999999994</v>
+        <v>87.807500000000005</v>
       </c>
       <c r="J5" s="21">
         <v>100</v>
@@ -7069,27 +7118,27 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>68</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>246</v>
+        <v>70</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <v>33.067</v>
+        <v>32.134500000000003</v>
       </c>
       <c r="F6" s="21">
-        <v>36.189</v>
+        <v>40.400399999999998</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21">
-        <v>36.729999999999997</v>
+        <v>51.23</v>
       </c>
       <c r="I6" s="21">
-        <v>77.48</v>
+        <v>87.807500000000005</v>
       </c>
       <c r="J6" s="21">
         <v>100</v>
@@ -7100,27 +7149,27 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <v>46.883299999999998</v>
+        <v>24.203299999999999</v>
       </c>
       <c r="F7" s="21">
-        <v>58.943100000000001</v>
+        <v>30.428999999999998</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21">
-        <v>44.17</v>
+        <v>32</v>
       </c>
       <c r="I7" s="21">
-        <v>86.042500000000004</v>
+        <v>83</v>
       </c>
       <c r="J7" s="21">
         <v>100</v>
@@ -7131,26 +7180,27 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>274</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="21">
-        <v>50.2301</v>
+        <v>61.559600000000003</v>
       </c>
       <c r="F8" s="21">
-        <v>63.150799999999997</v>
+        <v>77.394499999999994</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="21">
-        <v>49.16</v>
+        <v>47.15</v>
       </c>
       <c r="I8" s="21">
-        <v>87.29</v>
+        <v>86.787499999999994</v>
       </c>
       <c r="J8" s="21">
         <v>100</v>
@@ -7161,27 +7211,27 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>245</v>
+        <v>109</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="21">
-        <v>26.687100000000001</v>
+        <v>45.488199999999999</v>
       </c>
       <c r="F9" s="21">
-        <v>33.5518</v>
+        <v>57.189</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21">
-        <v>64.599999999999994</v>
+        <v>46.28</v>
       </c>
       <c r="I9" s="21">
-        <v>91.15</v>
+        <v>86.57</v>
       </c>
       <c r="J9" s="21">
         <v>100</v>
@@ -7192,27 +7242,27 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="21">
-        <v>45.488199999999999</v>
+        <v>51.510399999999997</v>
       </c>
       <c r="F10" s="21">
-        <v>57.189</v>
+        <v>64.760300000000001</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="21">
-        <v>46.28</v>
+        <v>55.77</v>
       </c>
       <c r="I10" s="21">
-        <v>86.57</v>
+        <v>88.942499999999995</v>
       </c>
       <c r="J10" s="21">
         <v>100</v>
@@ -7223,27 +7273,26 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>73</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>281</v>
+      </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="21">
-        <v>35.300699999999999</v>
+        <v>54.305300000000003</v>
       </c>
       <c r="F11" s="21">
-        <v>44.381100000000004</v>
+        <v>68.274299999999997</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21">
-        <v>39.450000000000003</v>
+        <v>53.44</v>
       </c>
       <c r="I11" s="21">
-        <v>84.862499999999997</v>
+        <v>88.36</v>
       </c>
       <c r="J11" s="21">
         <v>100</v>
@@ -7254,27 +7303,27 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="21">
-        <v>32.134500000000003</v>
+        <v>61.559600000000003</v>
       </c>
       <c r="F12" s="21">
-        <v>40.400399999999998</v>
+        <v>77.394499999999994</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="21">
-        <v>51.23</v>
+        <v>47.15</v>
       </c>
       <c r="I12" s="21">
-        <v>87.807500000000005</v>
+        <v>86.787499999999994</v>
       </c>
       <c r="J12" s="21">
         <v>100</v>
@@ -7285,27 +7334,27 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>75</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>116</v>
+        <v>77</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>236</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="21">
-        <v>54.305300000000003</v>
+        <v>33.067</v>
       </c>
       <c r="F13" s="21">
-        <v>68.274299999999997</v>
+        <v>36.189</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21">
-        <v>53.44</v>
+        <v>36.729999999999997</v>
       </c>
       <c r="I13" s="21">
-        <v>88.36</v>
+        <v>77.48</v>
       </c>
       <c r="J13" s="21">
         <v>100</v>
@@ -7316,27 +7365,27 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>76</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>252</v>
+        <v>78</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="21">
-        <v>44.709000000000003</v>
+        <v>35.300699999999999</v>
       </c>
       <c r="F14" s="21">
-        <v>50.756999999999998</v>
+        <v>44.381100000000004</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21">
-        <v>49.16</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="I14" s="21">
-        <v>87.55</v>
+        <v>84.862499999999997</v>
       </c>
       <c r="J14" s="21">
         <v>100</v>
@@ -7347,27 +7396,26 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="1"/>
+        <v>259</v>
+      </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="21">
-        <v>24.203299999999999</v>
+        <v>50.2301</v>
       </c>
       <c r="F15" s="21">
-        <v>30.428999999999998</v>
+        <v>63.150799999999997</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21">
-        <v>32</v>
+        <v>49.16</v>
       </c>
       <c r="I15" s="21">
-        <v>83</v>
+        <v>87.29</v>
       </c>
       <c r="J15" s="21">
         <v>100</v>
@@ -7378,27 +7426,27 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>78</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>112</v>
+        <v>80</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>241</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="21">
-        <v>25.194400000000002</v>
+        <v>44.709000000000003</v>
       </c>
       <c r="F16" s="21">
-        <v>31.6751</v>
+        <v>50.756999999999998</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="21">
-        <v>29.07</v>
+        <v>49.16</v>
       </c>
       <c r="I16" s="21">
-        <v>82.267499999999998</v>
+        <v>87.55</v>
       </c>
       <c r="J16" s="21">
         <v>100</v>
@@ -7409,27 +7457,27 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="21">
-        <v>51.510399999999997</v>
+        <v>54.305300000000003</v>
       </c>
       <c r="F17" s="21">
-        <v>64.760300000000001</v>
+        <v>68.274299999999997</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21">
-        <v>55.77</v>
+        <v>53.44</v>
       </c>
       <c r="I17" s="21">
-        <v>88.942499999999995</v>
+        <v>88.36</v>
       </c>
       <c r="J17" s="21">
         <v>100</v>
@@ -7440,27 +7488,27 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="21">
-        <v>32.134500000000003</v>
+        <v>26.687100000000001</v>
       </c>
       <c r="F18" s="21">
-        <v>40.400399999999998</v>
+        <v>33.5518</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21">
-        <v>51.23</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="I18" s="21">
-        <v>87.807500000000005</v>
+        <v>91.15</v>
       </c>
       <c r="J18" s="21">
         <v>100</v>
@@ -7471,27 +7519,26 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>269</v>
+      </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="21">
-        <v>61.559600000000003</v>
+        <v>37</v>
       </c>
       <c r="F19" s="21">
-        <v>77.394499999999994</v>
+        <v>61</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21">
-        <v>47.15</v>
+        <v>59</v>
       </c>
       <c r="I19" s="21">
-        <v>86.787499999999994</v>
+        <v>87</v>
       </c>
       <c r="J19" s="21">
         <v>100</v>
@@ -7502,26 +7549,27 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>82</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>296</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="1"/>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="21">
-        <v>54.305300000000003</v>
+        <v>25.992799999999999</v>
       </c>
       <c r="F20" s="21">
-        <v>68.274299999999997</v>
+        <v>32.678899999999999</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21">
-        <v>53.44</v>
+        <v>39.1</v>
       </c>
       <c r="I20" s="21">
-        <v>88.36</v>
+        <v>84.775000000000006</v>
       </c>
       <c r="J20" s="21">
         <v>100</v>
@@ -7532,26 +7580,27 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>284</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C21" s="1"/>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="21">
-        <v>37</v>
+        <v>52.380499999999998</v>
       </c>
       <c r="F21" s="21">
-        <v>61</v>
+        <v>65.854299999999995</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="21">
-        <v>59</v>
+        <v>31.45</v>
       </c>
       <c r="I21" s="21">
-        <v>87</v>
+        <v>82.862499999999997</v>
       </c>
       <c r="J21" s="21">
         <v>100</v>
@@ -7561,6 +7610,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K21">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -7570,7 +7624,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -7584,7 +7638,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D1" s="1">
         <v>0</v>
@@ -7610,10 +7664,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>84</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>152</v>
+        <v>86</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -7640,26 +7694,26 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3" s="21">
-        <v>46</v>
+        <v>30.539000000000001</v>
       </c>
       <c r="F3" s="21">
-        <v>56</v>
+        <v>38.394500000000001</v>
       </c>
       <c r="G3" s="21"/>
       <c r="H3" s="21">
-        <v>41.83</v>
+        <v>65.2</v>
       </c>
       <c r="I3" s="21">
-        <v>85.457499999999996</v>
+        <v>91.3</v>
       </c>
       <c r="J3" s="21">
         <v>100</v>
@@ -7670,56 +7724,41 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>86</v>
-      </c>
-      <c r="B4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="21">
-        <v>47</v>
-      </c>
-      <c r="F4" s="21">
-        <v>59</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="21"/>
-      <c r="H4" s="21">
-        <v>67.150000000000006</v>
-      </c>
-      <c r="I4" s="21">
-        <v>91.787499999999994</v>
-      </c>
-      <c r="J4" s="21">
-        <v>100</v>
-      </c>
-      <c r="K4" s="21">
-        <v>100</v>
-      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <v>46.0959</v>
+        <v>31.7163</v>
       </c>
       <c r="F5" s="21">
-        <v>57.953099999999999</v>
+        <v>39.874600000000001</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21">
-        <v>45.2</v>
+        <v>48.38</v>
       </c>
       <c r="I5" s="21">
-        <v>86.3</v>
+        <v>87.094999999999999</v>
       </c>
       <c r="J5" s="21">
         <v>100</v>
@@ -7730,26 +7769,26 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <v>54.484000000000002</v>
+        <v>43.461500000000001</v>
       </c>
       <c r="F6" s="21">
-        <v>68.498900000000006</v>
+        <v>54.640999999999998</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21">
-        <v>45.16</v>
+        <v>88.79</v>
       </c>
       <c r="I6" s="21">
-        <v>86.29</v>
+        <v>97.197500000000005</v>
       </c>
       <c r="J6" s="21">
         <v>100</v>
@@ -7760,26 +7799,26 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <v>50.2301</v>
+        <v>35.718299999999999</v>
       </c>
       <c r="F7" s="21">
-        <v>63.150799999999997</v>
+        <v>44.906100000000002</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21">
-        <v>49.16</v>
+        <v>55.43</v>
       </c>
       <c r="I7" s="21">
-        <v>87.29</v>
+        <v>88.857500000000002</v>
       </c>
       <c r="J7" s="21">
         <v>100</v>
@@ -7790,26 +7829,26 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="21">
-        <v>30.539000000000001</v>
+        <v>29.882999999999999</v>
       </c>
       <c r="F8" s="21">
-        <v>38.394500000000001</v>
+        <v>37.569699999999997</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="21">
-        <v>65.2</v>
+        <v>48.28</v>
       </c>
       <c r="I8" s="21">
-        <v>91.3</v>
+        <v>87.07</v>
       </c>
       <c r="J8" s="21">
         <v>100</v>
@@ -7820,10 +7859,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -7850,7 +7889,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
         <v>153</v>
@@ -7878,12 +7917,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -7910,26 +7949,26 @@
     </row>
     <row r="12" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="21">
-        <v>43.461500000000001</v>
+        <v>54.484000000000002</v>
       </c>
       <c r="F12" s="21">
-        <v>54.640999999999998</v>
+        <v>68.498900000000006</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="21">
-        <v>88.79</v>
+        <v>45.16</v>
       </c>
       <c r="I12" s="21">
-        <v>97.197500000000005</v>
+        <v>86.29</v>
       </c>
       <c r="J12" s="21">
         <v>100</v>
@@ -7940,26 +7979,26 @@
     </row>
     <row r="13" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="21">
-        <v>29.882999999999999</v>
+        <v>46</v>
       </c>
       <c r="F13" s="21">
-        <v>37.569699999999997</v>
+        <v>56</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21">
-        <v>48.28</v>
+        <v>41.83</v>
       </c>
       <c r="I13" s="21">
-        <v>87.07</v>
+        <v>85.457499999999996</v>
       </c>
       <c r="J13" s="21">
         <v>100</v>
@@ -7970,26 +8009,26 @@
     </row>
     <row r="14" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="21">
-        <v>35.718299999999999</v>
+        <v>50.2301</v>
       </c>
       <c r="F14" s="21">
-        <v>44.906100000000002</v>
+        <v>63.150799999999997</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21">
-        <v>55.43</v>
+        <v>49.16</v>
       </c>
       <c r="I14" s="21">
-        <v>88.857500000000002</v>
+        <v>87.29</v>
       </c>
       <c r="J14" s="21">
         <v>100</v>
@@ -8000,41 +8039,56 @@
     </row>
     <row r="15" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>97</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="21">
+        <v>47</v>
+      </c>
+      <c r="F15" s="21">
+        <v>59</v>
+      </c>
       <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
+      <c r="H15" s="21">
+        <v>67.150000000000006</v>
+      </c>
+      <c r="I15" s="21">
+        <v>91.787499999999994</v>
+      </c>
+      <c r="J15" s="21">
+        <v>100</v>
+      </c>
+      <c r="K15" s="21">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="21">
-        <v>26.2437</v>
+        <v>46.0959</v>
       </c>
       <c r="F16" s="21">
-        <v>32.994300000000003</v>
+        <v>57.953099999999999</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="21">
-        <v>55.49</v>
+        <v>45.2</v>
       </c>
       <c r="I16" s="21">
-        <v>88.872500000000002</v>
+        <v>86.3</v>
       </c>
       <c r="J16" s="21">
         <v>100</v>
@@ -8043,28 +8097,28 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>99</v>
-      </c>
-      <c r="B17" t="s">
-        <v>119</v>
+        <v>101</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>152</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="21">
-        <v>29.882999999999999</v>
+        <v>40.459299999999999</v>
       </c>
       <c r="F17" s="21">
-        <v>37.569699999999997</v>
+        <v>50.866599999999998</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21">
-        <v>48.28</v>
+        <v>63.44</v>
       </c>
       <c r="I17" s="21">
-        <v>87.07</v>
+        <v>90.86</v>
       </c>
       <c r="J17" s="21">
         <v>100</v>
@@ -8075,26 +8129,26 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="21">
-        <v>31.7163</v>
+        <v>46</v>
       </c>
       <c r="F18" s="21">
-        <v>39.874600000000001</v>
+        <v>56</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21">
-        <v>48.38</v>
+        <v>41.83</v>
       </c>
       <c r="I18" s="21">
-        <v>87.094999999999999</v>
+        <v>85.457499999999996</v>
       </c>
       <c r="J18" s="21">
         <v>100</v>
@@ -8105,26 +8159,26 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>101</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>121</v>
+        <v>103</v>
+      </c>
+      <c r="B19" t="s">
+        <v>119</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="21">
-        <v>40.459299999999999</v>
+        <v>29.882999999999999</v>
       </c>
       <c r="F19" s="21">
-        <v>50.866599999999998</v>
+        <v>37.569699999999997</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21">
-        <v>63.44</v>
+        <v>48.28</v>
       </c>
       <c r="I19" s="21">
-        <v>90.86</v>
+        <v>87.07</v>
       </c>
       <c r="J19" s="21">
         <v>100</v>
@@ -8135,26 +8189,26 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>102</v>
-      </c>
-      <c r="B20" t="s">
-        <v>122</v>
+        <v>104</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>233</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="21">
-        <v>46</v>
+        <v>26.2437</v>
       </c>
       <c r="F20" s="21">
-        <v>56</v>
+        <v>32.994300000000003</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21">
-        <v>41.83</v>
+        <v>55.49</v>
       </c>
       <c r="I20" s="21">
-        <v>85.457499999999996</v>
+        <v>88.872500000000002</v>
       </c>
       <c r="J20" s="21">
         <v>100</v>
@@ -8165,10 +8219,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>103</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>243</v>
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
+        <v>147</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -8193,27 +8247,22 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="16"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="16"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="16"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0400-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K21">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8223,7 +8272,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.25" style="9" customWidth="1"/>
@@ -8236,9 +8285,9 @@
     <col min="12" max="16384" width="8.625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D1" s="17">
         <v>0</v>
@@ -8262,29 +8311,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
-        <v>104</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="20">
         <v>0</v>
       </c>
       <c r="E2" s="22">
-        <v>69.8</v>
+        <v>41.1325</v>
       </c>
       <c r="F2" s="22">
-        <v>80.5</v>
+        <v>51.712899999999998</v>
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="22">
-        <v>85.38</v>
+        <v>51.88</v>
       </c>
       <c r="I2" s="22">
-        <v>94.29</v>
+        <v>87.97</v>
       </c>
       <c r="J2" s="22">
         <v>100</v>
@@ -8293,29 +8342,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="20">
         <v>0</v>
       </c>
       <c r="E3" s="22">
-        <v>54.199199999999998</v>
+        <v>47.265099999999997</v>
       </c>
       <c r="F3" s="22">
-        <v>68.140799999999999</v>
+        <v>59.423000000000002</v>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="22">
-        <v>42.3</v>
+        <v>48.78</v>
       </c>
       <c r="I3" s="22">
-        <v>85.575000000000003</v>
+        <v>87.194999999999993</v>
       </c>
       <c r="J3" s="22">
         <v>100</v>
@@ -8324,29 +8373,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="20">
         <v>0</v>
       </c>
       <c r="E4" s="22">
-        <v>47.265099999999997</v>
+        <v>54.199199999999998</v>
       </c>
       <c r="F4" s="22">
-        <v>59.423000000000002</v>
+        <v>68.140799999999999</v>
       </c>
       <c r="G4" s="22"/>
       <c r="H4" s="22">
-        <v>48.78</v>
+        <v>42.3</v>
       </c>
       <c r="I4" s="22">
-        <v>87.194999999999993</v>
+        <v>85.575000000000003</v>
       </c>
       <c r="J4" s="22">
         <v>100</v>
@@ -8355,29 +8404,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>39</v>
+        <v>245</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="20">
         <v>0</v>
       </c>
       <c r="E5" s="22">
-        <v>41.1325</v>
+        <v>56.826935768367747</v>
       </c>
       <c r="F5" s="22">
-        <v>51.712899999999998</v>
+        <v>67.659799133658922</v>
       </c>
       <c r="G5" s="22"/>
       <c r="H5" s="22">
-        <v>51.88</v>
+        <v>47.36</v>
       </c>
       <c r="I5" s="22">
-        <v>87.97</v>
+        <v>83.6</v>
       </c>
       <c r="J5" s="22">
         <v>100</v>
@@ -8386,29 +8435,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="20">
         <v>0</v>
       </c>
       <c r="E6" s="22">
-        <v>25.0868</v>
+        <v>26.835752770392673</v>
       </c>
       <c r="F6" s="22">
-        <v>33.0764</v>
+        <v>35.942168788085553</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22">
-        <v>48.55</v>
+        <v>35.53</v>
       </c>
       <c r="I6" s="22">
-        <v>90.15</v>
+        <v>70.430000000000007</v>
       </c>
       <c r="J6" s="22">
         <v>100</v>
@@ -8417,29 +8466,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
-        <v>109</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>255</v>
+        <v>111</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="20">
         <v>0</v>
       </c>
       <c r="E7" s="22">
-        <v>26.835752770392673</v>
+        <v>69.8</v>
       </c>
       <c r="F7" s="22">
-        <v>35.942168788085553</v>
+        <v>80.5</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22">
-        <v>35.53</v>
+        <v>85.38</v>
       </c>
       <c r="I7" s="22">
-        <v>70.430000000000007</v>
+        <v>94.29</v>
       </c>
       <c r="J7" s="22">
         <v>100</v>
@@ -8448,29 +8497,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>256</v>
+        <v>171</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="20">
         <v>0</v>
       </c>
       <c r="E8" s="22">
-        <v>56.826935768367747</v>
+        <v>25.0868</v>
       </c>
       <c r="F8" s="22">
-        <v>67.659799133658922</v>
+        <v>33.0764</v>
       </c>
       <c r="G8" s="22"/>
       <c r="H8" s="22">
-        <v>47.36</v>
+        <v>48.55</v>
       </c>
       <c r="I8" s="22">
-        <v>83.6</v>
+        <v>90.15</v>
       </c>
       <c r="J8" s="22">
         <v>100</v>
@@ -8479,29 +8528,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
+        <v>113</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>111</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>149</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="20">
         <v>0</v>
       </c>
       <c r="E9" s="22">
-        <v>26.570799999999998</v>
+        <v>20</v>
       </c>
       <c r="F9" s="22">
-        <v>33.4056</v>
+        <v>27</v>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="22">
-        <v>36.32</v>
+        <v>51.14</v>
       </c>
       <c r="I9" s="22">
-        <v>70.040000000000006</v>
+        <v>93.95</v>
       </c>
       <c r="J9" s="22">
         <v>100</v>
@@ -8510,9 +8559,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>93</v>
@@ -8541,29 +8590,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="20">
         <v>0</v>
       </c>
       <c r="E11" s="22">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11" s="22">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G11" s="22"/>
       <c r="H11" s="22">
-        <v>51.14</v>
+        <v>44.65</v>
       </c>
       <c r="I11" s="22">
-        <v>93.95</v>
+        <v>89.86</v>
       </c>
       <c r="J11" s="22">
         <v>100</v>
@@ -8572,29 +8621,29 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="20">
         <v>0</v>
       </c>
       <c r="E12" s="22">
-        <v>18</v>
+        <v>26.570799999999998</v>
       </c>
       <c r="F12" s="22">
-        <v>23</v>
+        <v>33.4056</v>
       </c>
       <c r="G12" s="22"/>
       <c r="H12" s="22">
-        <v>44.65</v>
+        <v>36.32</v>
       </c>
       <c r="I12" s="22">
-        <v>89.86</v>
+        <v>70.040000000000006</v>
       </c>
       <c r="J12" s="22">
         <v>100</v>
@@ -8603,9 +8652,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>110</v>
@@ -8634,23 +8683,68 @@
         <v>100</v>
       </c>
     </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S14" s="18"/>
+      <c r="T14" s="18"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+    </row>
+    <row r="17" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+    </row>
+    <row r="18" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="S18" s="18"/>
+      <c r="T18" s="18"/>
+    </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
       <c r="S19" s="18"/>
       <c r="T19" s="18"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
       <c r="S20" s="18"/>
       <c r="T20" s="18"/>
     </row>
     <row r="21" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
       <c r="S21" s="18"/>
       <c r="T21" s="18"/>
     </row>
     <row r="22" spans="4:20" x14ac:dyDescent="0.3">
-      <c r="S22" s="41"/>
-      <c r="T22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
     </row>
     <row r="23" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
       <c r="S23" s="18"/>
       <c r="T23" s="18"/>
     </row>
@@ -8667,8 +8761,8 @@
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
       <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
       <c r="S25" s="18"/>
       <c r="T25" s="18"/>
     </row>
@@ -8678,8 +8772,6 @@
       <c r="F26" s="41"/>
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
     </row>
     <row r="27" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D27" s="41"/>
@@ -8687,8 +8779,6 @@
       <c r="F27" s="41"/>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
-      <c r="S27" s="18"/>
-      <c r="T27" s="18"/>
     </row>
     <row r="28" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D28" s="41"/>
@@ -8696,62 +8786,26 @@
       <c r="F28" s="41"/>
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-    </row>
-    <row r="29" spans="4:20" x14ac:dyDescent="0.3">
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-    </row>
-    <row r="30" spans="4:20" x14ac:dyDescent="0.3">
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-    </row>
-    <row r="31" spans="4:20" x14ac:dyDescent="0.3">
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-    </row>
-    <row r="32" spans="4:20" x14ac:dyDescent="0.3">
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-    </row>
-    <row r="33" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0500-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K13">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="12">
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D26:F26"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -8776,7 +8830,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D1" s="17">
         <v>0</v>
@@ -8802,10 +8856,10 @@
     </row>
     <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="C2"/>
       <c r="D2" s="1">
@@ -8833,10 +8887,10 @@
     </row>
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C3"/>
       <c r="D3" s="1">
@@ -8864,10 +8918,10 @@
     </row>
     <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C4"/>
       <c r="D4" s="1">
@@ -8895,7 +8949,7 @@
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>202</v>
@@ -8926,7 +8980,7 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>203</v>
@@ -8957,10 +9011,10 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
@@ -8988,10 +9042,10 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -9018,10 +9072,10 @@
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
@@ -9049,7 +9103,7 @@
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>205</v>
@@ -9080,7 +9134,7 @@
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>206</v>
@@ -9111,7 +9165,7 @@
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>200</v>
@@ -9142,7 +9196,7 @@
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>201</v>
@@ -9355,6 +9409,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="D26:F26"/>
@@ -9363,12 +9423,6 @@
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -9393,7 +9447,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D1" s="17">
         <v>0</v>
@@ -9419,10 +9473,10 @@
     </row>
     <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>214</v>
+        <v>130</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>283</v>
       </c>
       <c r="C2"/>
       <c r="D2" s="1">
@@ -9450,10 +9504,10 @@
     </row>
     <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>215</v>
+        <v>131</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>284</v>
       </c>
       <c r="C3"/>
       <c r="D3" s="1">
@@ -9481,10 +9535,10 @@
     </row>
     <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="C4"/>
       <c r="D4" s="1">
@@ -9512,27 +9566,27 @@
     </row>
     <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>216</v>
+        <v>133</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>291</v>
       </c>
       <c r="C5"/>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <v>39.355384081844988</v>
+        <v>61.697195012427166</v>
       </c>
       <c r="F5" s="21">
-        <v>66.234610716143578</v>
+        <v>71.465569456337846</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21">
-        <v>54.86</v>
+        <v>40.64</v>
       </c>
       <c r="I5" s="21">
-        <v>86.25</v>
+        <v>81.28</v>
       </c>
       <c r="J5" s="21">
         <v>100</v>
@@ -9543,27 +9597,27 @@
     </row>
     <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C6" s="1"/>
+        <v>134</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6"/>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <v>69.17465859900031</v>
+        <v>39.355384081844988</v>
       </c>
       <c r="F6" s="21">
-        <v>72.740535240236298</v>
+        <v>66.234610716143578</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21">
-        <v>38.85</v>
+        <v>54.86</v>
       </c>
       <c r="I6" s="21">
-        <v>75.150000000000006</v>
+        <v>86.25</v>
       </c>
       <c r="J6" s="21">
         <v>100</v>
@@ -9574,27 +9628,27 @@
     </row>
     <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <v>55.362691736763971</v>
+        <v>69.17465859900031</v>
       </c>
       <c r="F7" s="21">
-        <v>67.346857991093515</v>
+        <v>72.740535240236298</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21">
-        <v>50</v>
+        <v>38.85</v>
       </c>
       <c r="I7" s="21">
-        <v>82.57</v>
+        <v>75.150000000000006</v>
       </c>
       <c r="J7" s="21">
         <v>100</v>
@@ -9605,27 +9659,27 @@
     </row>
     <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="21">
-        <v>64.587216815525537</v>
+        <v>55.362691736763971</v>
       </c>
       <c r="F8" s="21">
-        <v>75.641274887641103</v>
+        <v>67.346857991093515</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="21">
-        <v>32.93</v>
+        <v>50</v>
       </c>
       <c r="I8" s="21">
-        <v>68.38</v>
+        <v>82.57</v>
       </c>
       <c r="J8" s="21">
         <v>100</v>
@@ -9636,27 +9690,27 @@
     </row>
     <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>250</v>
+        <v>137</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>292</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="21">
-        <v>63.952217751949533</v>
+        <v>56.467445440550577</v>
       </c>
       <c r="F9" s="21">
-        <v>74.171757810559782</v>
+        <v>70.325998370008151</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21">
-        <v>47</v>
+        <v>35.11</v>
       </c>
       <c r="I9" s="21">
-        <v>84.52</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="J9" s="21">
         <v>100</v>
@@ -9667,120 +9721,120 @@
     </row>
     <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="20">
-        <v>0</v>
-      </c>
-      <c r="E10" s="22">
-        <v>61.042303520362886</v>
-      </c>
-      <c r="F10" s="22">
-        <v>72.935607928212221</v>
-      </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22">
-        <v>49.06</v>
-      </c>
-      <c r="I10" s="22">
-        <v>83.73</v>
-      </c>
-      <c r="J10" s="22">
-        <v>100</v>
-      </c>
-      <c r="K10" s="22">
+        <v>138</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21">
+        <v>64.587216815525537</v>
+      </c>
+      <c r="F10" s="21">
+        <v>75.641274887641103</v>
+      </c>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21">
+        <v>32.93</v>
+      </c>
+      <c r="I10" s="21">
+        <v>68.38</v>
+      </c>
+      <c r="J10" s="21">
+        <v>100</v>
+      </c>
+      <c r="K10" s="21">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="20">
-        <v>0</v>
-      </c>
-      <c r="E11" s="22">
-        <v>79.407506222648806</v>
-      </c>
-      <c r="F11" s="22">
-        <v>84.979583204542138</v>
-      </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22">
-        <v>54.82</v>
-      </c>
-      <c r="I11" s="22">
-        <v>87.07</v>
-      </c>
-      <c r="J11" s="22">
-        <v>100</v>
-      </c>
-      <c r="K11" s="22">
+        <v>139</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21">
+        <v>63.952217751949533</v>
+      </c>
+      <c r="F11" s="21">
+        <v>74.171757810559782</v>
+      </c>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21">
+        <v>47</v>
+      </c>
+      <c r="I11" s="21">
+        <v>84.52</v>
+      </c>
+      <c r="J11" s="21">
+        <v>100</v>
+      </c>
+      <c r="K11" s="21">
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>219</v>
-      </c>
-      <c r="C12"/>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="21">
-        <v>67.604991600671937</v>
-      </c>
-      <c r="F12" s="21">
-        <v>81.381489480841523</v>
-      </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21">
-        <v>54.25</v>
-      </c>
-      <c r="I12" s="21">
-        <v>86.48</v>
-      </c>
-      <c r="J12" s="21">
-        <v>100</v>
-      </c>
-      <c r="K12" s="21">
+        <v>140</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="20">
+        <v>0</v>
+      </c>
+      <c r="E12" s="22">
+        <v>61.042303520362886</v>
+      </c>
+      <c r="F12" s="22">
+        <v>72.935607928212221</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22">
+        <v>49.06</v>
+      </c>
+      <c r="I12" s="22">
+        <v>83.73</v>
+      </c>
+      <c r="J12" s="22">
+        <v>100</v>
+      </c>
+      <c r="K12" s="22">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="20">
         <v>0</v>
       </c>
       <c r="E13" s="22">
-        <v>35.410884755437458</v>
+        <v>79.407506222648806</v>
       </c>
       <c r="F13" s="22">
-        <v>56.908768821966341</v>
+        <v>84.979583204542138</v>
       </c>
       <c r="G13" s="22"/>
       <c r="H13" s="22">
-        <v>39.979999999999997</v>
+        <v>54.82</v>
       </c>
       <c r="I13" s="22">
-        <v>75.430000000000007</v>
+        <v>87.07</v>
       </c>
       <c r="J13" s="22">
         <v>100</v>
@@ -9791,27 +9845,27 @@
     </row>
     <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>221</v>
+        <v>142</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>289</v>
       </c>
       <c r="C14"/>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="21">
-        <v>61.697195012427166</v>
+        <v>67.604991600671937</v>
       </c>
       <c r="F14" s="21">
-        <v>71.465569456337846</v>
+        <v>81.381489480841523</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21">
-        <v>40.64</v>
+        <v>54.25</v>
       </c>
       <c r="I14" s="21">
-        <v>81.28</v>
+        <v>86.48</v>
       </c>
       <c r="J14" s="21">
         <v>100</v>
@@ -9822,27 +9876,27 @@
     </row>
     <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="1"/>
+        <v>143</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C15"/>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="21">
-        <v>56.467445440550577</v>
+        <v>58.546547283208639</v>
       </c>
       <c r="F15" s="21">
-        <v>70.325998370008151</v>
+        <v>65.58444744265914</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21">
-        <v>35.11</v>
+        <v>46.13</v>
       </c>
       <c r="I15" s="21">
-        <v>73.599999999999994</v>
+        <v>83.76</v>
       </c>
       <c r="J15" s="21">
         <v>100</v>
@@ -9853,58 +9907,58 @@
     </row>
     <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="21">
-        <v>46.913769751693003</v>
-      </c>
-      <c r="F16" s="21">
-        <v>55.444695259593679</v>
-      </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21">
-        <v>46.27</v>
-      </c>
-      <c r="I16" s="21">
-        <v>82.65</v>
-      </c>
-      <c r="J16" s="21">
-        <v>100</v>
-      </c>
-      <c r="K16" s="21">
+        <v>144</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="20">
+        <v>0</v>
+      </c>
+      <c r="E16" s="22">
+        <v>35.410884755437458</v>
+      </c>
+      <c r="F16" s="22">
+        <v>56.908768821966341</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22">
+        <v>39.979999999999997</v>
+      </c>
+      <c r="I16" s="22">
+        <v>75.430000000000007</v>
+      </c>
+      <c r="J16" s="22">
+        <v>100</v>
+      </c>
+      <c r="K16" s="22">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17"/>
+        <v>145</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="C17" s="1"/>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="21">
-        <v>58.546547283208639</v>
+        <v>46.913769751693003</v>
       </c>
       <c r="F17" s="21">
-        <v>65.58444744265914</v>
+        <v>55.444695259593679</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21">
-        <v>46.13</v>
+        <v>46.27</v>
       </c>
       <c r="I17" s="21">
-        <v>83.76</v>
+        <v>82.65</v>
       </c>
       <c r="J17" s="21">
         <v>100</v>
@@ -10049,6 +10103,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="D26:F26"/>
@@ -10057,12 +10117,6 @@
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -10142,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="D3" s="15">
         <v>30</v>
@@ -10321,7 +10375,7 @@
         <v>70</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="K7" s="15">
         <v>63.150799999999997</v>
@@ -10342,7 +10396,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="D8" s="15">
         <v>80.382000000000005</v>
@@ -10361,7 +10415,7 @@
         <v>71</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="K8" s="15">
         <v>33.5518</v>
@@ -10502,7 +10556,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="D12" s="15">
         <v>62.060099999999998</v>
@@ -10801,7 +10855,7 @@
         <v>82</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="K19" s="15">
         <v>68.274299999999997</v>
@@ -10841,7 +10895,7 @@
         <v>83</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="K20" s="30">
         <v>61</v>
@@ -10942,7 +10996,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="D23" s="30">
         <v>78</v>
@@ -11222,7 +11276,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="D30" s="15">
         <v>64.800799999999995</v>
@@ -11241,7 +11295,7 @@
         <v>93</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="K30" s="15">
         <v>37</v>
@@ -11401,7 +11455,7 @@
         <v>97</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="K34" s="15">
         <v>35</v>
@@ -11641,7 +11695,7 @@
         <v>103</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="K40" s="15">
         <v>32.994300000000003</v>
@@ -11681,7 +11735,7 @@
         <v>104</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="K41" s="15">
         <v>81</v>
@@ -11881,7 +11935,7 @@
         <v>109</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="K46" s="15">
         <v>36</v>
@@ -11921,7 +11975,7 @@
         <v>110</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="K47" s="15">
         <v>68</v>
@@ -12161,7 +12215,7 @@
         <v>116</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="K53" s="15">
         <v>30</v>
@@ -12240,7 +12294,7 @@
         <v>118</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="K55" s="15">
         <v>73</v>
@@ -12396,7 +12450,7 @@
         <v>122</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="K59" s="15">
         <v>40.484000000000002</v>
@@ -12417,7 +12471,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="D60" s="15">
         <v>62</v>
@@ -12456,7 +12510,7 @@
         <v>59</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="D61" s="15">
         <v>67</v>
@@ -12552,7 +12606,7 @@
         <v>126</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="K63" s="15">
         <v>23</v>
@@ -12591,7 +12645,7 @@
         <v>127</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="K64" s="15">
         <v>21</v>
@@ -12665,7 +12719,7 @@
         <v>129</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="K66" s="15">
         <v>49</v>
@@ -12704,7 +12758,7 @@
         <v>130</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="K67" s="15">
         <v>63</v>

--- a/반응성 염료 상용성 실험.xlsx
+++ b/반응성 염료 상용성 실험.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\Ohyoung Dye Finder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1548A5A-047F-4DE7-A492-264912F21232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD601CFB-310F-4639-9A9C-0D7113606BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="802" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="802" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="그래프" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="295">
   <si>
     <t>Sunfix Red FE-6BA</t>
   </si>
@@ -1168,6 +1168,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> H-E6GN</t>
     </r>
@@ -1192,6 +1194,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> H-E4G</t>
     </r>
@@ -1220,6 +1224,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> H-ER</t>
     </r>
@@ -1252,6 +1258,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> H-ER 150%</t>
     </r>
@@ -1280,6 +1288,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> H-EL</t>
     </r>
@@ -1312,6 +1322,8 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve"> H-ELN</t>
     </r>
@@ -5797,7 +5809,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.125" style="4" customWidth="1"/>
@@ -5836,27 +5848,27 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1">
         <v>0</v>
       </c>
       <c r="E2" s="21">
-        <v>48.580599999999997</v>
+        <v>33.6432</v>
       </c>
       <c r="F2" s="21">
-        <v>61.076900000000002</v>
+        <v>42.297199999999997</v>
       </c>
       <c r="G2" s="21"/>
       <c r="H2" s="21">
-        <v>83.65</v>
+        <v>61.37</v>
       </c>
       <c r="I2" s="21">
-        <v>95.912499999999994</v>
+        <v>90.342500000000001</v>
       </c>
       <c r="J2" s="21">
         <v>100</v>
@@ -5867,27 +5879,27 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3" s="21">
-        <v>48.580599999999997</v>
+        <v>41</v>
       </c>
       <c r="F3" s="21">
-        <v>61.076900000000002</v>
+        <v>42</v>
       </c>
       <c r="G3" s="21"/>
       <c r="H3" s="21">
-        <v>83.65</v>
+        <v>52</v>
       </c>
       <c r="I3" s="21">
-        <v>95.912499999999994</v>
+        <v>87</v>
       </c>
       <c r="J3" s="21">
         <v>100</v>
@@ -5898,27 +5910,27 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="21">
-        <v>33.6432</v>
+        <v>28.882400000000001</v>
       </c>
       <c r="F4" s="21">
-        <v>42.297199999999997</v>
+        <v>36.311799999999998</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21">
-        <v>61.37</v>
+        <v>41.77</v>
       </c>
       <c r="I4" s="21">
-        <v>90.342500000000001</v>
+        <v>85.442499999999995</v>
       </c>
       <c r="J4" s="21">
         <v>100</v>
@@ -5929,27 +5941,27 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="21">
-        <v>41</v>
+        <v>36.441800000000001</v>
       </c>
       <c r="F5" s="21">
-        <v>42</v>
+        <v>45.8157</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21">
-        <v>52</v>
+        <v>53.81</v>
       </c>
       <c r="I5" s="21">
-        <v>87</v>
+        <v>88.452500000000001</v>
       </c>
       <c r="J5" s="21">
         <v>100</v>
@@ -5960,27 +5972,27 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="21">
-        <v>28.882400000000001</v>
+        <v>36.665900000000001</v>
       </c>
       <c r="F6" s="21">
-        <v>36.311799999999998</v>
+        <v>46.097499999999997</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21">
-        <v>41.77</v>
+        <v>37.78</v>
       </c>
       <c r="I6" s="21">
-        <v>85.442499999999995</v>
+        <v>84.444999999999993</v>
       </c>
       <c r="J6" s="21">
         <v>100</v>
@@ -5991,27 +6003,27 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <v>36.441800000000001</v>
+        <v>41.466200000000001</v>
       </c>
       <c r="F7" s="21">
-        <v>45.8157</v>
+        <v>52.1325</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21">
-        <v>53.81</v>
+        <v>82.92</v>
       </c>
       <c r="I7" s="21">
-        <v>88.452500000000001</v>
+        <v>95.73</v>
       </c>
       <c r="J7" s="21">
         <v>100</v>
@@ -6022,27 +6034,27 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="21">
-        <v>36.665900000000001</v>
+        <v>44.933100000000003</v>
       </c>
       <c r="F8" s="21">
-        <v>46.097499999999997</v>
+        <v>56.491199999999999</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="21">
-        <v>37.78</v>
+        <v>84.7</v>
       </c>
       <c r="I8" s="21">
-        <v>84.444999999999993</v>
+        <v>96.174999999999997</v>
       </c>
       <c r="J8" s="21">
         <v>100</v>
@@ -6053,27 +6065,27 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>38</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="21">
-        <v>41.466200000000001</v>
+        <v>49.476599999999998</v>
       </c>
       <c r="F9" s="21">
-        <v>52.1325</v>
+        <v>62.203400000000002</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21">
-        <v>82.92</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="I9" s="21">
-        <v>95.73</v>
+        <v>91.724999999999994</v>
       </c>
       <c r="J9" s="21">
         <v>100</v>
@@ -6084,27 +6096,27 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="21">
-        <v>44.933100000000003</v>
+        <v>35.834800000000001</v>
       </c>
       <c r="F10" s="21">
-        <v>56.491199999999999</v>
+        <v>45.052500000000002</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="21">
-        <v>84.7</v>
+        <v>51.65</v>
       </c>
       <c r="I10" s="21">
-        <v>96.174999999999997</v>
+        <v>87.912499999999994</v>
       </c>
       <c r="J10" s="21">
         <v>100</v>
@@ -6115,27 +6127,27 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>40</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>26</v>
+        <v>42</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="21">
-        <v>49.476599999999998</v>
+        <v>38.585900000000002</v>
       </c>
       <c r="F11" s="21">
-        <v>62.203400000000002</v>
+        <v>48.511299999999999</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21">
-        <v>66.900000000000006</v>
+        <v>46.21</v>
       </c>
       <c r="I11" s="21">
-        <v>91.724999999999994</v>
+        <v>86.552499999999995</v>
       </c>
       <c r="J11" s="21">
         <v>100</v>
@@ -6146,27 +6158,27 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="21">
-        <v>35.834800000000001</v>
+        <v>41.556899999999999</v>
       </c>
       <c r="F12" s="21">
-        <v>45.052500000000002</v>
+        <v>52.246499999999997</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="21">
-        <v>51.65</v>
+        <v>61.16</v>
       </c>
       <c r="I12" s="21">
-        <v>87.912499999999994</v>
+        <v>90.29</v>
       </c>
       <c r="J12" s="21">
         <v>100</v>
@@ -6177,27 +6189,27 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="21">
-        <v>38.585900000000002</v>
+        <v>45.353900000000003</v>
       </c>
       <c r="F13" s="21">
-        <v>48.511299999999999</v>
+        <v>57.020299999999999</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21">
-        <v>46.21</v>
+        <v>67.77</v>
       </c>
       <c r="I13" s="21">
-        <v>86.552499999999995</v>
+        <v>91.942499999999995</v>
       </c>
       <c r="J13" s="21">
         <v>100</v>
@@ -6208,27 +6220,27 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="21">
-        <v>41.556899999999999</v>
+        <v>40.878300000000003</v>
       </c>
       <c r="F14" s="21">
-        <v>52.246499999999997</v>
+        <v>51.3934</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21">
-        <v>61.16</v>
+        <v>71.94</v>
       </c>
       <c r="I14" s="21">
-        <v>90.29</v>
+        <v>92.984999999999999</v>
       </c>
       <c r="J14" s="21">
         <v>100</v>
@@ -6239,27 +6251,27 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="21">
-        <v>45.353900000000003</v>
+        <v>36.901600000000002</v>
       </c>
       <c r="F15" s="21">
-        <v>57.020299999999999</v>
+        <v>46.393700000000003</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21">
-        <v>67.77</v>
+        <v>57.01</v>
       </c>
       <c r="I15" s="21">
-        <v>91.942499999999995</v>
+        <v>89.252499999999998</v>
       </c>
       <c r="J15" s="21">
         <v>100</v>
@@ -6270,27 +6282,27 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="21">
-        <v>40.878300000000003</v>
+        <v>37.041899999999998</v>
       </c>
       <c r="F16" s="21">
-        <v>51.3934</v>
+        <v>46.570099999999996</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="21">
-        <v>71.94</v>
+        <v>38.119999999999997</v>
       </c>
       <c r="I16" s="21">
-        <v>92.984999999999999</v>
+        <v>84.53</v>
       </c>
       <c r="J16" s="21">
         <v>100</v>
@@ -6301,27 +6313,27 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="21">
-        <v>36.901600000000002</v>
+        <v>36.665900000000001</v>
       </c>
       <c r="F17" s="21">
-        <v>46.393700000000003</v>
+        <v>46.097499999999997</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21">
-        <v>57.01</v>
+        <v>37.78</v>
       </c>
       <c r="I17" s="21">
-        <v>89.252499999999998</v>
+        <v>84.444999999999993</v>
       </c>
       <c r="J17" s="21">
         <v>100</v>
@@ -6332,27 +6344,27 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="21">
-        <v>37.041899999999998</v>
+        <v>56.967300000000002</v>
       </c>
       <c r="F18" s="21">
-        <v>46.570099999999996</v>
+        <v>71.620999999999995</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="21">
-        <v>38.119999999999997</v>
+        <v>53.71</v>
       </c>
       <c r="I18" s="21">
-        <v>84.53</v>
+        <v>88.427499999999995</v>
       </c>
       <c r="J18" s="21">
         <v>100</v>
@@ -6363,27 +6375,27 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="21">
-        <v>36.665900000000001</v>
+        <v>36.877099999999999</v>
       </c>
       <c r="F19" s="21">
-        <v>46.097499999999997</v>
+        <v>46.362900000000003</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21">
-        <v>37.78</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="I19" s="21">
-        <v>84.444999999999993</v>
+        <v>85.2</v>
       </c>
       <c r="J19" s="21">
         <v>100</v>
@@ -6394,27 +6406,27 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="21">
-        <v>56.967300000000002</v>
+        <v>41</v>
       </c>
       <c r="F20" s="21">
-        <v>71.620999999999995</v>
+        <v>42</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="21">
-        <v>53.71</v>
+        <v>52</v>
       </c>
       <c r="I20" s="21">
-        <v>88.427499999999995</v>
+        <v>87</v>
       </c>
       <c r="J20" s="21">
         <v>100</v>
@@ -6425,58 +6437,57 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>50</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>267</v>
+      </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
-      <c r="E21" s="21">
-        <v>36.877099999999999</v>
-      </c>
-      <c r="F21" s="21">
-        <v>46.362900000000003</v>
-      </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21">
-        <v>40.799999999999997</v>
-      </c>
-      <c r="I21" s="21">
-        <v>85.2</v>
-      </c>
-      <c r="J21" s="21">
-        <v>100</v>
-      </c>
-      <c r="K21" s="21">
+      <c r="E21" s="29">
+        <v>54.9</v>
+      </c>
+      <c r="F21" s="29">
+        <v>67.2</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29">
+        <v>71</v>
+      </c>
+      <c r="I21" s="29">
+        <v>95.1</v>
+      </c>
+      <c r="J21" s="29">
+        <v>100</v>
+      </c>
+      <c r="K21" s="29">
         <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="21">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F22" s="21">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="21">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I22" s="21">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J22" s="21">
         <v>100</v>
@@ -6487,57 +6498,58 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>52</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>267</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="1"/>
       <c r="D23" s="1">
         <v>0</v>
       </c>
-      <c r="E23" s="29">
-        <v>54.9</v>
-      </c>
-      <c r="F23" s="29">
-        <v>67.2</v>
-      </c>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29">
-        <v>71</v>
-      </c>
-      <c r="I23" s="29">
-        <v>95.1</v>
-      </c>
-      <c r="J23" s="29">
-        <v>100</v>
-      </c>
-      <c r="K23" s="29">
+      <c r="E23" s="21">
+        <v>43.008499999999998</v>
+      </c>
+      <c r="F23" s="21">
+        <v>54.071599999999997</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21">
+        <v>47.06</v>
+      </c>
+      <c r="I23" s="21">
+        <v>86.765000000000001</v>
+      </c>
+      <c r="J23" s="21">
+        <v>100</v>
+      </c>
+      <c r="K23" s="21">
         <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>252</v>
+        <v>144</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="21">
-        <v>57</v>
+        <v>36.441800000000001</v>
       </c>
       <c r="F24" s="21">
-        <v>62</v>
+        <v>45.8157</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="21">
-        <v>60</v>
+        <v>53.81</v>
       </c>
       <c r="I24" s="21">
-        <v>92</v>
+        <v>88.452500000000001</v>
       </c>
       <c r="J24" s="21">
         <v>100</v>
@@ -6548,27 +6560,27 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>54</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>88</v>
+        <v>56</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="21">
-        <v>43.008499999999998</v>
+        <v>38.787199999999999</v>
       </c>
       <c r="F25" s="21">
-        <v>54.071599999999997</v>
+        <v>48.764400000000002</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="21">
-        <v>47.06</v>
+        <v>52.94</v>
       </c>
       <c r="I25" s="21">
-        <v>86.765000000000001</v>
+        <v>88.234999999999999</v>
       </c>
       <c r="J25" s="21">
         <v>100</v>
@@ -6579,27 +6591,27 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="21">
-        <v>36.441800000000001</v>
+        <v>51.4009</v>
       </c>
       <c r="F26" s="21">
-        <v>45.8157</v>
+        <v>64.622699999999995</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="21">
-        <v>53.81</v>
+        <v>52.84</v>
       </c>
       <c r="I26" s="21">
-        <v>88.452500000000001</v>
+        <v>88.21</v>
       </c>
       <c r="J26" s="21">
         <v>100</v>
@@ -6610,27 +6622,27 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>56</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>27</v>
+        <v>58</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>254</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="21">
-        <v>38.787199999999999</v>
+        <v>54</v>
       </c>
       <c r="F27" s="21">
-        <v>48.764400000000002</v>
+        <v>68</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="21">
-        <v>52.94</v>
+        <v>49</v>
       </c>
       <c r="I27" s="21">
-        <v>88.234999999999999</v>
+        <v>90</v>
       </c>
       <c r="J27" s="21">
         <v>100</v>
@@ -6641,27 +6653,26 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="1"/>
+        <v>78</v>
+      </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="21">
-        <v>51.4009</v>
+        <v>23</v>
       </c>
       <c r="F28" s="21">
-        <v>64.622699999999995</v>
+        <v>33</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="21">
-        <v>52.84</v>
+        <v>57</v>
       </c>
       <c r="I28" s="21">
-        <v>88.21</v>
+        <v>90</v>
       </c>
       <c r="J28" s="21">
         <v>100</v>
@@ -6672,27 +6683,27 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>58</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>254</v>
+        <v>60</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="21">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F29" s="21">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="21">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I29" s="21">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J29" s="21">
         <v>100</v>
@@ -6703,26 +6714,27 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="C30" s="1"/>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="21">
-        <v>23</v>
+        <v>48.580599999999997</v>
       </c>
       <c r="F30" s="21">
-        <v>33</v>
+        <v>61.076900000000002</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="21">
-        <v>57</v>
+        <v>83.65</v>
       </c>
       <c r="I30" s="21">
-        <v>90</v>
+        <v>95.912499999999994</v>
       </c>
       <c r="J30" s="21">
         <v>100</v>
@@ -6733,27 +6745,27 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="21">
-        <v>53</v>
+        <v>48.580599999999997</v>
       </c>
       <c r="F31" s="21">
-        <v>67</v>
+        <v>61.076900000000002</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="21">
-        <v>45</v>
+        <v>83.65</v>
       </c>
       <c r="I31" s="21">
-        <v>84</v>
+        <v>95.912499999999994</v>
       </c>
       <c r="J31" s="21">
         <v>100</v>
@@ -6764,27 +6776,27 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="21">
-        <v>48.580599999999997</v>
+        <v>38.895400000000002</v>
       </c>
       <c r="F32" s="21">
-        <v>61.076900000000002</v>
+        <v>48.900399999999998</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="21">
-        <v>83.65</v>
+        <v>33.89</v>
       </c>
       <c r="I32" s="21">
-        <v>95.912499999999994</v>
+        <v>83.472499999999997</v>
       </c>
       <c r="J32" s="21">
         <v>100</v>
@@ -6795,27 +6807,27 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="21">
-        <v>48.580599999999997</v>
+        <v>54.240299999999998</v>
       </c>
       <c r="F33" s="21">
-        <v>61.076900000000002</v>
+        <v>68.192499999999995</v>
       </c>
       <c r="G33" s="21"/>
       <c r="H33" s="21">
-        <v>83.65</v>
+        <v>67.239999999999995</v>
       </c>
       <c r="I33" s="21">
-        <v>95.912499999999994</v>
+        <v>91.81</v>
       </c>
       <c r="J33" s="21">
         <v>100</v>
@@ -6826,27 +6838,27 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="21">
-        <v>38.895400000000002</v>
+        <v>33.547600000000003</v>
       </c>
       <c r="F34" s="21">
-        <v>48.900399999999998</v>
+        <v>42.177</v>
       </c>
       <c r="G34" s="21"/>
       <c r="H34" s="21">
-        <v>33.89</v>
+        <v>51.67</v>
       </c>
       <c r="I34" s="21">
-        <v>83.472499999999997</v>
+        <v>87.917500000000004</v>
       </c>
       <c r="J34" s="21">
         <v>100</v>
@@ -6855,89 +6867,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>64</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1">
-        <v>0</v>
-      </c>
-      <c r="E35" s="21">
-        <v>54.240299999999998</v>
-      </c>
-      <c r="F35" s="21">
-        <v>68.192499999999995</v>
-      </c>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21">
-        <v>67.239999999999995</v>
-      </c>
-      <c r="I35" s="21">
-        <v>91.81</v>
-      </c>
-      <c r="J35" s="21">
-        <v>100</v>
-      </c>
-      <c r="K35" s="21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>65</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1">
-        <v>0</v>
-      </c>
-      <c r="E36" s="21">
-        <v>33.547600000000003</v>
-      </c>
-      <c r="F36" s="21">
-        <v>42.177</v>
-      </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21">
-        <v>51.67</v>
-      </c>
-      <c r="I36" s="21">
-        <v>87.917500000000004</v>
-      </c>
-      <c r="J36" s="21">
-        <v>100</v>
-      </c>
-      <c r="K36" s="21">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="19"/>
-      <c r="C46" s="1"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
-      <c r="K46" s="21"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="19"/>
-      <c r="C47" s="1"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="19"/>
+      <c r="C44" s="1"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="19"/>
+      <c r="C45" s="1"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0200-000000000000}">
@@ -8794,11 +8744,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="12">
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="D27:F27"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
@@ -8806,6 +8751,11 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="D26:F26"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="D27:F27"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -9409,12 +9359,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="D26:F26"/>
@@ -9423,6 +9367,12 @@
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -10103,12 +10053,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:H25"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="D26:F26"/>
@@ -10117,6 +10061,12 @@
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:H25"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
